--- a/AP/AP Template.xlsx
+++ b/AP/AP Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MSIG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\e y ka dai\MSIGSX\AP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:19_{7E781577-4DA5-4F4E-AE17-7A61258BAE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C151A1A6-9A2F-4B0F-983A-DABAF5F0C3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="495" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="495" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="H" sheetId="1" r:id="rId1"/>
@@ -5520,7 +5520,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="510">
   <si>
     <t>DocNum</t>
   </si>
@@ -7047,6 +7047,9 @@
   </si>
   <si>
     <t>ລູກຄ້າປະກັນໄພລົດພາກສະໜັກໃຈ</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -9414,7 +9417,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D4E935-59F6-461A-B8F8-D1041556EDFB}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.8984375" bestFit="1" customWidth="1"/>
@@ -9424,7 +9427,7 @@
     <col min="13" max="13" width="10.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>306</v>
       </c>
@@ -9464,8 +9467,11 @@
       <c r="M1" s="1" t="s">
         <v>503</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>449</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -9505,8 +9511,11 @@
       <c r="M2" s="1" t="s">
         <v>503</v>
       </c>
+      <c r="N2" s="1" t="s">
+        <v>449</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>260500007</v>
       </c>
@@ -9546,18 +9555,10 @@
       <c r="M3" s="6" t="s">
         <v>506</v>
       </c>
+      <c r="N3" s="6" t="s">
+        <v>509</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:13" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:13" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:13" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:13" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:13" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:13" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:13" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:13" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:13" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:13" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/AP/AP Template.xlsx
+++ b/AP/AP Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\e y ka dai\MSIGSX\AP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MSIGSX\MSIGSX\AP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C151A1A6-9A2F-4B0F-983A-DABAF5F0C3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75242F09-46B0-47A3-93B3-4F78D81DD451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="495" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-1560" windowWidth="30936" windowHeight="16776" tabRatio="495" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="H" sheetId="1" r:id="rId1"/>
@@ -2950,7 +2950,7 @@
     <author>Zhao, Peggy</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{8B5D05D0-2480-4923-9E34-BC9523CF3A90}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{DE99D2F7-5A88-48FE-936C-659155D1C228}">
       <text>
         <r>
           <rPr>
@@ -2967,7 +2967,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{135C2083-282A-4428-8714-97E6916309F9}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{FD091CEF-1111-4D0A-A4B6-02BE8B45393C}">
       <text>
         <r>
           <rPr>
@@ -2984,7 +2984,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{3B1C9484-B68E-4444-ACF1-BAFE7F9331F3}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{7E4C9609-3A41-4EBC-AC92-0C6784B8D63C}">
       <text>
         <r>
           <rPr>
@@ -3001,7 +3001,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{5C0D3D35-CA1E-40A4-83C1-1895EE9AE139}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{01918DC9-FA87-404F-B51A-097A39F863D8}">
       <text>
         <r>
           <rPr>
@@ -3019,7 +3019,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{8D1B5D9A-D36D-4FF1-B94D-16F887BACADC}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{6FEDF0A2-322C-40B2-821F-27039F9E7B0F}">
       <text>
         <r>
           <rPr>
@@ -3037,7 +3037,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{DD18CA93-125F-49AF-8B6F-A9EA2DAADBAC}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{7A3EC35E-A94E-4439-B671-BC16BE7525D3}">
       <text>
         <r>
           <rPr>
@@ -3055,7 +3055,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{1C9DC4FE-1C3C-40B2-8D90-0138198BEA84}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{5442D29B-664F-489F-B21C-82A23D0DACC8}">
       <text>
         <r>
           <rPr>
@@ -3072,7 +3072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{203EDEF5-CEC3-4E8E-AE07-501332ED7360}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{D1B093F4-2D3A-49E9-A317-1C26BE81A156}">
       <text>
         <r>
           <rPr>
@@ -3089,7 +3089,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{766175C9-12B9-4DC9-BC87-A6556A41F00F}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{3EA5342D-18C4-4497-918B-D29B87857551}">
       <text>
         <r>
           <rPr>
@@ -3107,7 +3107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{2BC8F667-202D-4783-932A-33A884764A04}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{8942D7C8-78F6-48D3-BED4-D9781E2BAC4C}">
       <text>
         <r>
           <rPr>
@@ -5344,7 +5344,7 @@
     <author>Zhao, Peggy</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{2B4A566D-11B6-4AB4-ACCB-9949E7DC6CEB}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{999762BA-8304-4B51-BD48-0948D8E9F111}">
       <text>
         <r>
           <rPr>
@@ -5362,7 +5362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{AB01D48A-32DB-4266-86A3-2108A93353D3}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{5ADC4FDB-137F-4815-A949-033719B83803}">
       <text>
         <r>
           <rPr>
@@ -5379,7 +5379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{38393E5B-A8A7-49F4-B186-E45B1F569A20}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{DBCD5790-4B98-4A13-8833-19421B00665D}">
       <text>
         <r>
           <rPr>
@@ -5396,7 +5396,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{D2BE058C-18D0-41C1-AEC7-40C493D7643A}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{CD22D40C-6782-4EEE-9160-EB3964AB3F2F}">
       <text>
         <r>
           <rPr>
@@ -5413,7 +5413,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{47AE0A51-A12F-4BB1-B0A9-8A621952CF01}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{46AD6A61-789F-48AC-9BD1-473CC1B58507}">
       <text>
         <r>
           <rPr>
@@ -5431,7 +5431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{608612FC-8596-47C0-ABEE-DAAC2076269E}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{6821DD45-8A3D-428E-B637-3DA26C4D296F}">
       <text>
         <r>
           <rPr>
@@ -5449,7 +5449,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{4E141287-281F-470A-AA43-78EF57002656}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{E6F9EDD6-9EB7-4576-981C-D4287DA5E9F9}">
       <text>
         <r>
           <rPr>
@@ -5466,7 +5466,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{968F03DB-5EA7-4ADA-89CB-4E7B47767908}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{F0778E13-40C3-47EA-86E1-F18C0DCECB2E}">
       <text>
         <r>
           <rPr>
@@ -5483,7 +5483,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{A0FCAE6E-A63D-4229-8AA9-7C7FBFD07B76}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{25E9F2A4-5F0F-4B37-8E58-A57F2DA7D79D}">
       <text>
         <r>
           <rPr>
@@ -5501,7 +5501,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{DD0B8A1D-7376-451F-862E-F444872E80B9}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{1F5E8EC4-8708-42D7-8000-C9465EF40917}">
       <text>
         <r>
           <rPr>
@@ -5520,7 +5520,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="534">
   <si>
     <t>DocNum</t>
   </si>
@@ -6437,9 +6437,6 @@
     <t>niiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiii</t>
   </si>
   <si>
-    <t>May 13, 2026</t>
-  </si>
-  <si>
     <t>ParentKey</t>
   </si>
   <si>
@@ -7050,13 +7047,88 @@
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>ເລກທີ່ເອກະສານ</t>
+  </si>
+  <si>
+    <t>ລະຫັດສິນຄ້າ</t>
+  </si>
+  <si>
+    <t>ລາຍລະອຽດສິນຄ້າ</t>
+  </si>
+  <si>
+    <t>ຈຳນວນ</t>
+  </si>
+  <si>
+    <t>ລາຄາ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ລະຫັດສາງສິນຄ້າ </t>
+  </si>
+  <si>
+    <t>ອມພ</t>
+  </si>
+  <si>
+    <t>ຍອດລວມ</t>
+  </si>
+  <si>
+    <t>ຍອດ ອມພ</t>
+  </si>
+  <si>
+    <t>ສະກຸນເງິນ</t>
+  </si>
+  <si>
+    <t>ຊ່ອງທາງ</t>
+  </si>
+  <si>
+    <t>ປະເພດລາຍຈ່າຍປະກັນໄພ</t>
+  </si>
+  <si>
+    <t>ປະເພດການເຄລມ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> WHT</t>
+  </si>
+  <si>
+    <t>20260513</t>
+  </si>
+  <si>
+    <t>ເລກລຳດັບໃນລະບົບ</t>
+  </si>
+  <si>
+    <t>ປະເພດເອກະສານ</t>
+  </si>
+  <si>
+    <t>ວັນທີບັນທຶກເອກະສານ</t>
+  </si>
+  <si>
+    <t>ວັນຄົບກຳນົດການຊຳລະ</t>
+  </si>
+  <si>
+    <t>ລະຫັດຄູ່ຄ້າ</t>
+  </si>
+  <si>
+    <t>ຊື່ຄູ່ຄ້າ</t>
+  </si>
+  <si>
+    <t>ຍອດລວມຂອງເອກະສານ</t>
+  </si>
+  <si>
+    <t>ລະຫັດຊຸດຂໍ້ມູນ</t>
+  </si>
+  <si>
+    <t>ເລກທີ່ສັນຍາ</t>
+  </si>
+  <si>
+    <t>ຊື່ເຈົ້າຂອງສັນຍາ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7094,12 +7166,26 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <u/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Phetsarath OT"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Phetsarath OT"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Phetsarath OT"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7142,6 +7228,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -7155,19 +7259,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8490,138 +8621,186 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:HZ13"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.796875" customWidth="1"/>
-    <col min="5" max="5" width="12.3984375" customWidth="1"/>
-    <col min="6" max="6" width="15.296875" customWidth="1"/>
-    <col min="7" max="7" width="19.59765625" customWidth="1"/>
-    <col min="8" max="8" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.8984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.8984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.796875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:234" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:234" x14ac:dyDescent="0.5">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="19" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:234" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:234" x14ac:dyDescent="0.5">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="13" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:234" ht="15.6" x14ac:dyDescent="0.4">
-      <c r="A3">
+    <row r="3" spans="1:234" x14ac:dyDescent="0.5">
+      <c r="A3" s="10">
         <v>260500007</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="20">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="E3" t="s">
-        <v>305</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D3" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>508</v>
-      </c>
-      <c r="H3">
+      <c r="G3" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="H3" s="10">
         <v>560000</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="10">
         <v>110</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="10">
         <v>56</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="10" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:234" x14ac:dyDescent="0.25">
-      <c r="B7" s="4"/>
+    <row r="4" spans="1:234" x14ac:dyDescent="0.5">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
     </row>
-    <row r="12" spans="1:234" x14ac:dyDescent="0.25">
-      <c r="B12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="AL12" s="4"/>
-      <c r="BE12" s="4"/>
-      <c r="BG12" s="4"/>
+    <row r="5" spans="1:234" x14ac:dyDescent="0.5">
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
     </row>
-    <row r="13" spans="1:234" x14ac:dyDescent="0.25">
-      <c r="AO13" s="4"/>
-      <c r="HY13" s="4"/>
-      <c r="HZ13" s="4"/>
+    <row r="6" spans="1:234" x14ac:dyDescent="0.5">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+    </row>
+    <row r="7" spans="1:234" s="25" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="23" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>525</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>526</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>528</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>530</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>531</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>532</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="12" spans="1:234" x14ac:dyDescent="0.5">
+      <c r="B12" s="26"/>
+      <c r="R12" s="26"/>
+      <c r="Y12" s="26"/>
+      <c r="AL12" s="26"/>
+      <c r="BE12" s="26"/>
+      <c r="BG12" s="26"/>
+    </row>
+    <row r="13" spans="1:234" x14ac:dyDescent="0.5">
+      <c r="AO13" s="26"/>
+      <c r="HY13" s="26"/>
+      <c r="HZ13" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8638,125 +8817,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:128" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="AO1" s="1" t="s">
         <v>297</v>
@@ -8765,262 +8944,262 @@
         <v>298</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AR1" s="1" t="s">
         <v>294</v>
       </c>
       <c r="AS1" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="AT1" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="AX1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="AY1" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="BI1" s="1" t="s">
         <v>87</v>
       </c>
       <c r="BJ1" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="BK1" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="BU1" s="1" t="s">
         <v>46</v>
       </c>
       <c r="BV1" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="BW1" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="CI1" s="1" t="s">
         <v>293</v>
       </c>
       <c r="CJ1" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="CK1" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="DA1" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="DH1" s="1" t="s">
-        <v>408</v>
       </c>
       <c r="DI1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="DJ1" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="DK1" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="DK1" s="1" t="s">
+      <c r="DL1" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DM1" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="DM1" s="1" t="s">
+      <c r="DN1" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="DN1" s="1" t="s">
+      <c r="DO1" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="DO1" s="1" t="s">
+      <c r="DP1" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="DP1" s="1" t="s">
+      <c r="DQ1" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="DQ1" s="1" t="s">
+      <c r="DR1" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="DR1" s="1" t="s">
+      <c r="DS1" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="DS1" s="1" t="s">
+      <c r="DT1" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="DT1" s="1" t="s">
+      <c r="DU1" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="DU1" s="1" t="s">
+      <c r="DV1" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="DV1" s="1" t="s">
+      <c r="DW1" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="DW1" s="1" t="s">
+      <c r="DX1" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="DX1" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:128" x14ac:dyDescent="0.25">
@@ -9028,121 +9207,121 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="D2" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="I2" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="N2" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="P2" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>75</v>
       </c>
       <c r="W2" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="Z2" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="X2" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="AB2" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="AA2" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="AH2" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="AG2" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="AI2" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>440</v>
-      </c>
       <c r="AK2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="AL2" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="AO2" s="2" t="s">
         <v>297</v>
@@ -9151,7 +9330,7 @@
         <v>298</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AR2" s="2" t="s">
         <v>294</v>
@@ -9160,253 +9339,253 @@
         <v>295</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AU2" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="AW2" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="AX2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="AY2" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="AZ2" s="2" t="s">
-        <v>351</v>
-      </c>
       <c r="BA2" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="BB2" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="BC2" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="BE2" s="2" t="s">
         <v>296</v>
       </c>
       <c r="BF2" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="BG2" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BH2" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="BI2" s="2" t="s">
         <v>88</v>
       </c>
       <c r="BJ2" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="BK2" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BL2" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="BM2" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="BL2" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="BM2" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="BN2" s="2" t="s">
         <v>292</v>
       </c>
       <c r="BO2" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="BP2" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="BP2" s="2" t="s">
+      <c r="BQ2" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="BS2" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="BQ2" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="BR2" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BT2" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="BT2" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="BU2" s="2" t="s">
         <v>46</v>
       </c>
       <c r="BV2" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="BW2" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="BY2" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="BZ2" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="CA2" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="BW2" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="BX2" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="BY2" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="BZ2" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="CA2" s="2" t="s">
+      <c r="CB2" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="CC2" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="CD2" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="CB2" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="CC2" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CE2" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CF2" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CG2" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="CG2" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="CH2" s="2" t="s">
         <v>293</v>
       </c>
       <c r="CI2" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="CJ2" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CK2" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="CK2" s="2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CM2" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="CM2" s="2" t="s">
+      <c r="CN2" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CO2" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="CO2" s="2" t="s">
+      <c r="CP2" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="CP2" s="2" t="s">
+      <c r="CQ2" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="CR2" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="CQ2" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="CR2" s="2" t="s">
+      <c r="CS2" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="CS2" s="2" t="s">
+      <c r="CT2" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="CT2" s="2" t="s">
+      <c r="CU2" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="CU2" s="2" t="s">
+      <c r="CV2" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="CV2" s="2" t="s">
+      <c r="CW2" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="CW2" s="2" t="s">
+      <c r="CX2" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="CX2" s="2" t="s">
+      <c r="CY2" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="CY2" s="2" t="s">
+      <c r="CZ2" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="CZ2" s="2" t="s">
+      <c r="DA2" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="DA2" s="2" t="s">
+      <c r="DB2" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="DB2" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="DC2" s="2" t="s">
         <v>240</v>
       </c>
       <c r="DD2" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="DE2" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="DE2" s="2" t="s">
+      <c r="DF2" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="DF2" s="2" t="s">
+      <c r="DG2" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="DG2" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="DH2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="DJ2" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="DK2" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="DL2" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="DK2" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="DL2" s="2" t="s">
+      <c r="DM2" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="DM2" s="2" t="s">
+      <c r="DN2" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="DN2" s="2" t="s">
+      <c r="DO2" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="DO2" s="2" t="s">
+      <c r="DP2" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="DQ2" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="DP2" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="DQ2" s="2" t="s">
+      <c r="DR2" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="DR2" s="2" t="s">
+      <c r="DS2" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="DS2" s="2" t="s">
+      <c r="DT2" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="DU2" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="DT2" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="DU2" s="2" t="s">
+      <c r="DV2" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="DV2" s="2" t="s">
+      <c r="DW2" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="DW2" s="2" t="s">
+      <c r="DX2" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="DX2" s="2" t="s">
-        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -9417,146 +9596,209 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D4E935-59F6-461A-B8F8-D1041556EDFB}">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.796875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="A1" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="E1" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="8" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="A2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="A3" s="10">
+        <v>260500007</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="D3" s="10">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10">
+        <v>560000</v>
+      </c>
+      <c r="F3" s="12">
+        <v>1</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="H3" s="10">
+        <v>560000</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="K3" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>449</v>
+      <c r="L3" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>508</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>449</v>
-      </c>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="F4" s="12"/>
     </row>
-    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.4">
-      <c r="A3">
-        <v>260500007</v>
-      </c>
-      <c r="B3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>560000</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>500</v>
-      </c>
-      <c r="H3">
-        <v>560000</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="J3" t="s">
-        <v>303</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="N3" s="6" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="F6" s="12"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="A7" s="16" t="s">
         <v>509</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>513</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>519</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/AP/AP Template.xlsx
+++ b/AP/AP Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MSIGSX\MSIGSX\AP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\e y ka dai\MSIGSX\AP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75242F09-46B0-47A3-93B3-4F78D81DD451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DD9125-4DD7-452E-ABC2-B1EEE1B490B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-1560" windowWidth="30936" windowHeight="16776" tabRatio="495" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="495" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="H" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="L" sheetId="3" r:id="rId3"/>
     <sheet name="OPCH - AP Line" sheetId="5" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'OPCH - AP Haed'!$A$1:$J$9</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2967,24 +2970,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{FD091CEF-1111-4D0A-A4B6-02BE8B45393C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Description: Internal Number_x000D_
-Type: long_x000D_
-Field Length: 11_x000D_
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{7E4C9609-3A41-4EBC-AC92-0C6784B8D63C}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{7E4C9609-3A41-4EBC-AC92-0C6784B8D63C}">
       <text>
         <r>
           <rPr>
@@ -3001,7 +2987,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{01918DC9-FA87-404F-B51A-097A39F863D8}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{01918DC9-FA87-404F-B51A-097A39F863D8}">
       <text>
         <r>
           <rPr>
@@ -3019,7 +3005,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{6FEDF0A2-322C-40B2-821F-27039F9E7B0F}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{6FEDF0A2-322C-40B2-821F-27039F9E7B0F}">
       <text>
         <r>
           <rPr>
@@ -3037,7 +3023,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{7A3EC35E-A94E-4439-B671-BC16BE7525D3}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{7A3EC35E-A94E-4439-B671-BC16BE7525D3}">
       <text>
         <r>
           <rPr>
@@ -3055,7 +3041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{5442D29B-664F-489F-B21C-82A23D0DACC8}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{5442D29B-664F-489F-B21C-82A23D0DACC8}">
       <text>
         <r>
           <rPr>
@@ -3072,7 +3058,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{D1B093F4-2D3A-49E9-A317-1C26BE81A156}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{D1B093F4-2D3A-49E9-A317-1C26BE81A156}">
       <text>
         <r>
           <rPr>
@@ -3089,7 +3075,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{3EA5342D-18C4-4497-918B-D29B87857551}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{3EA5342D-18C4-4497-918B-D29B87857551}">
       <text>
         <r>
           <rPr>
@@ -5520,7 +5506,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="536">
   <si>
     <t>DocNum</t>
   </si>
@@ -7094,9 +7080,6 @@
     <t>20260513</t>
   </si>
   <si>
-    <t>ເລກລຳດັບໃນລະບົບ</t>
-  </si>
-  <si>
     <t>ປະເພດເອກະສານ</t>
   </si>
   <si>
@@ -7122,6 +7105,15 @@
   </si>
   <si>
     <t>ຊື່ເຈົ້າຂອງສັນຍາ</t>
+  </si>
+  <si>
+    <t>(ຈຳເປັນຕ້ອງໃສ່ຈະຫລອດບໍ່ມີປ່ຽນ)</t>
+  </si>
+  <si>
+    <t>(ຈະປ່ຽນໄປຈາມແຈ່ລະເດືອນຈ້ອງເບິ່ງໃນລະບົບຕື່ມ)</t>
+  </si>
+  <si>
+    <t>01</t>
   </si>
 </sst>
 </file>
@@ -7230,12 +7222,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -7243,6 +7229,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7259,7 +7251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -7269,36 +7261,33 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8620,191 +8609,175 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:HZ13"/>
+  <dimension ref="A1:HY13"/>
   <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.59765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.296875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.8984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.09765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.3984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.8984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.796875" style="10"/>
+    <col min="1" max="1" width="12.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.796875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:234" x14ac:dyDescent="0.5">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:233" x14ac:dyDescent="0.5">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18" t="s">
+      <c r="B1" s="22" t="s">
         <v>2</v>
       </c>
+      <c r="C1" s="8" t="s">
+        <v>6</v>
+      </c>
       <c r="D1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:233" x14ac:dyDescent="0.5">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="G2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="H2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="I2" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="J2" s="11" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:234" x14ac:dyDescent="0.5">
-      <c r="A2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>300</v>
+    <row r="3" spans="1:233" x14ac:dyDescent="0.5">
+      <c r="A3" s="9">
+        <v>260500007</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>523</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>523</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="G3" s="9">
+        <v>560000</v>
+      </c>
+      <c r="H3" s="9">
+        <v>110</v>
+      </c>
+      <c r="I3" s="9">
+        <v>56</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>304</v>
       </c>
     </row>
-    <row r="3" spans="1:234" x14ac:dyDescent="0.5">
-      <c r="A3" s="10">
-        <v>260500007</v>
-      </c>
-      <c r="B3" s="20">
-        <v>24</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>523</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>523</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="H3" s="10">
-        <v>560000</v>
-      </c>
-      <c r="I3" s="10">
-        <v>110</v>
-      </c>
-      <c r="J3" s="10">
-        <v>56</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>304</v>
+    <row r="5" spans="1:233" x14ac:dyDescent="0.5">
+      <c r="A5" s="19" t="s">
+        <v>509</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>526</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>531</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>532</v>
       </c>
     </row>
-    <row r="4" spans="1:234" x14ac:dyDescent="0.5">
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
+    <row r="6" spans="1:233" x14ac:dyDescent="0.5">
+      <c r="B6" s="17" t="s">
+        <v>533</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>534</v>
+      </c>
     </row>
-    <row r="5" spans="1:234" x14ac:dyDescent="0.5">
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
+    <row r="7" spans="1:233" s="20" customFormat="1" x14ac:dyDescent="0.5"/>
+    <row r="12" spans="1:233" x14ac:dyDescent="0.5">
+      <c r="Q12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="AK12" s="21"/>
+      <c r="BD12" s="21"/>
+      <c r="BF12" s="21"/>
     </row>
-    <row r="6" spans="1:234" x14ac:dyDescent="0.5">
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-    </row>
-    <row r="7" spans="1:234" s="25" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="23" t="s">
-        <v>509</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>524</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>525</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>526</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>527</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>528</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>529</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>530</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>531</v>
-      </c>
-      <c r="J7" s="23" t="s">
-        <v>532</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="12" spans="1:234" x14ac:dyDescent="0.5">
-      <c r="B12" s="26"/>
-      <c r="R12" s="26"/>
-      <c r="Y12" s="26"/>
-      <c r="AL12" s="26"/>
-      <c r="BE12" s="26"/>
-      <c r="BG12" s="26"/>
-    </row>
-    <row r="13" spans="1:234" x14ac:dyDescent="0.5">
-      <c r="AO13" s="26"/>
-      <c r="HY13" s="26"/>
-      <c r="HZ13" s="26"/>
+    <row r="13" spans="1:233" x14ac:dyDescent="0.5">
+      <c r="AN13" s="21"/>
+      <c r="HX13" s="21"/>
+      <c r="HY13" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="39" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9596,24 +9569,24 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D4E935-59F6-461A-B8F8-D1041556EDFB}">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="11.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.09765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.09765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.59765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.09765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.09765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.796875" style="10"/>
+    <col min="1" max="1" width="12.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.796875" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.5">
@@ -9632,7 +9605,7 @@
       <c r="E1" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="22" t="s">
         <v>317</v>
       </c>
       <c r="G1" s="8" t="s">
@@ -9661,37 +9634,37 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="11" t="s">
         <v>500</v>
       </c>
       <c r="L2" s="8" t="s">
@@ -9705,104 +9678,110 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A3" s="10">
+      <c r="A3" s="9">
         <v>260500007</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>1</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <v>560000</v>
       </c>
-      <c r="F3" s="12">
-        <v>1</v>
-      </c>
-      <c r="G3" s="10" t="s">
+      <c r="F3" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <v>560000</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="12" t="s">
         <v>506</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="13" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="F4" s="12"/>
+      <c r="F4" s="23"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="F5" s="12"/>
+      <c r="F5" s="23"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="F6" s="12"/>
+      <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="14" t="s">
         <v>509</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
         <v>510</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="14" t="s">
         <v>511</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="14" t="s">
         <v>512</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="14" t="s">
         <v>513</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="14" t="s">
         <v>514</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="14" t="s">
         <v>515</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="14" t="s">
         <v>516</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="14" t="s">
         <v>517</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="14" t="s">
         <v>518</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="14" t="s">
         <v>519</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="14" t="s">
         <v>520</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="14" t="s">
         <v>521</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="14" t="s">
         <v>522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="F8" s="17" t="s">
+        <v>533</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/AP/AP Template.xlsx
+++ b/AP/AP Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\e y ka dai\MSIGSX\AP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DD9125-4DD7-452E-ABC2-B1EEE1B490B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACFDAEA-C99A-4529-8232-0935023597DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="495" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="495" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="H" sheetId="1" r:id="rId1"/>
@@ -7110,10 +7110,10 @@
     <t>(ຈຳເປັນຕ້ອງໃສ່ຈະຫລອດບໍ່ມີປ່ຽນ)</t>
   </si>
   <si>
-    <t>(ຈະປ່ຽນໄປຈາມແຈ່ລະເດືອນຈ້ອງເບິ່ງໃນລະບົບຕື່ມ)</t>
-  </si>
-  <si>
     <t>01</t>
+  </si>
+  <si>
+    <t>(ຈະປ່ຽນໄປຕາມແຕ່ລະເດືອນຈ້ອງເບິ່ງໃນລະບົບຕື່ມ)</t>
   </si>
 </sst>
 </file>
@@ -7251,7 +7251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -7283,11 +7283,6 @@
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8693,7 +8688,7 @@
       <c r="A3" s="9">
         <v>260500007</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="13" t="s">
         <v>301</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -8758,7 +8753,7 @@
         <v>533</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:233" s="20" customFormat="1" x14ac:dyDescent="0.5"/>
@@ -9693,8 +9688,8 @@
       <c r="E3" s="9">
         <v>560000</v>
       </c>
-      <c r="F3" s="25" t="s">
-        <v>535</v>
+      <c r="F3" s="12" t="s">
+        <v>534</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>499</v>
@@ -9720,15 +9715,6 @@
       <c r="N3" s="13" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="F4" s="23"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="F5" s="23"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A7" s="14" t="s">
